--- a/accountant-skill/data/Jan2026/general_ledger.xlsx
+++ b/accountant-skill/data/Jan2026/general_ledger.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="General Ledger" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Ledger" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -494,7 +494,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>1030</v>
+        <v>10000</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1110</v>
+        <v>11000</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>1320</v>
+        <v>13000</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>1610</v>
+        <v>15100</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>1611</v>
+        <v>15110</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1620</v>
+        <v>15200</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1621</v>
+        <v>15210</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1630</v>
+        <v>15300</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1631</v>
+        <v>15310</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1650</v>
+        <v>15300</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1651</v>
+        <v>15310</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>2060</v>
+        <v>21000</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>2100</v>
+        <v>25000</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>3010</v>
+        <v>31000</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3020</v>
+        <v>30200</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>3030</v>
+        <v>32000</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>4020</v>
+        <v>40000</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4030</v>
+        <v>40000</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>4040</v>
+        <v>40000</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>5110</v>
+        <v>62000</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>5210</v>
+        <v>63000</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>5220</v>
+        <v>65000</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>5400</v>
+        <v>65000</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>5420</v>
+        <v>65000</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>5500</v>
+        <v>64000</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>5600</v>
+        <v>60000</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>5700</v>
+        <v>65000</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>5800</v>
+        <v>67000</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>5920</v>
+        <v>65000</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1020</v>
+        <v>10100</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1030</v>
+        <v>10000</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1100</v>
+        <v>11000</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1110</v>
+        <v>11000</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1200</v>
+        <v>12000</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1320</v>
+        <v>13000</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>2010</v>
+        <v>20000</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>2030</v>
+        <v>22200</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3010</v>
+        <v>31000</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3020</v>
+        <v>30200</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>4010</v>
+        <v>40000</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>4020</v>
+        <v>40000</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>4020</v>
+        <v>40000</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>4020</v>
+        <v>40000</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>4020</v>
+        <v>40000</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>4020</v>
+        <v>40000</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>4030</v>
+        <v>40000</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>4030</v>
+        <v>40000</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>4030</v>
+        <v>40000</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>4030</v>
+        <v>40000</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>4040</v>
+        <v>40000</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
@@ -4424,7 +4424,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>4040</v>
+        <v>40000</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>4040</v>
+        <v>40000</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>4040</v>
+        <v>40000</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>5010</v>
+        <v>50000</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>5020</v>
+        <v>50100</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>5100</v>
+        <v>61000</v>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>5110</v>
+        <v>62000</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>5200</v>
+        <v>65000</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>5210</v>
+        <v>63000</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>5220</v>
+        <v>65000</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>5400</v>
+        <v>65000</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>5420</v>
+        <v>65000</v>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>5500</v>
+        <v>64000</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>5600</v>
+        <v>60000</v>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>5700</v>
+        <v>65000</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>5700</v>
+        <v>65000</v>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>5920</v>
+        <v>65000</v>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>

--- a/accountant-skill/data/Jan2026/general_ledger.xlsx
+++ b/accountant-skill/data/Jan2026/general_ledger.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5382,6 +5382,554 @@
       <c r="G164" s="3" t="n"/>
       <c r="H164" s="3" t="n"/>
     </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Work-in-Progress Inventory</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>OB</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Opening Balance</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="n"/>
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Work-in-Progress Inventory</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>JV-006</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>Opening WIP reversal</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="n"/>
+      <c r="G166" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Work-in-Progress Inventory</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>JV-011</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>Closing WIP per physical count</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G167" s="2" t="n"/>
+      <c r="H167" s="2" t="n">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>50300</v>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Opening Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>JV-006</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>Bring forward opening WIP</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>50300</v>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Opening Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>Clear to FG transfer</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="n"/>
+      <c r="G169" s="2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>50310</v>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>Closing Work-in-Progress</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>JV-011</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>Record closing WIP</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="n"/>
+      <c r="G170" s="2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>-65000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>JV-007</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Materials issued to production</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G171" s="2" t="n"/>
+      <c r="H171" s="2" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>50320</v>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Direct Materials Used</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>Clear to FG transfer</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="n"/>
+      <c r="G172" s="2" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>50330</v>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>Direct Labor Transferred to WIP</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>JV-008</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Labor allocated to WIP</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G173" s="2" t="n"/>
+      <c r="H173" s="2" t="n">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>50330</v>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>Direct Labor Transferred to WIP</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Clear to FG transfer</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="n"/>
+      <c r="G174" s="2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H174" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing Overhead Applied</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>JV-009</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Overhead applied to WIP</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G175" s="2" t="n"/>
+      <c r="H175" s="2" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing Overhead Applied</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>JV-009</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>Overhead applied to WIP</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G176" s="2" t="n"/>
+      <c r="H176" s="2" t="n">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing Overhead Applied</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>JV-009</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>Overhead applied to WIP</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G177" s="2" t="n"/>
+      <c r="H177" s="2" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>50340</v>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>Manufacturing Overhead Applied</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>Clear to FG transfer</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="n"/>
+      <c r="G178" s="2" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H178" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>50350</v>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>WIP Transferred to Finished Goods</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>JV-010</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>COGM - clearing WIP accumulation</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G179" s="2" t="n"/>
+      <c r="H179" s="2" t="n">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>12200</v>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>Inventory - Finished Goods</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>JV-012</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>COGM transferred to FG</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="n">
+        <v>260000</v>
+      </c>
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>50350</v>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>WIP Transferred to Finished Goods</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>JV-012</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>COGM transferred to FG - credit</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n"/>
+      <c r="G181" s="2" t="n">
+        <v>260000</v>
+      </c>
+      <c r="H181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n"/>
+      <c r="B182" s="3" t="n"/>
+      <c r="C182" s="3" t="n"/>
+      <c r="D182" s="3" t="n"/>
+      <c r="E182" s="3" t="n"/>
+      <c r="F182" s="2" t="n"/>
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
